--- a/output/tables/answers_eligibility_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_by_filing_match.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-27 12:52:48 EDT</t>
+    <t xml:space="preserve">2026-04-27 14:47:44 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Source data</t>

--- a/output/tables/answers_eligibility_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_by_filing_match.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-27 14:47:44 EDT</t>
+    <t xml:space="preserve">2026-04-27 15:58:44 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Source data</t>

--- a/output/tables/answers_eligibility_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_by_filing_match.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Generated at</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-27 15:58:44 EDT</t>
+    <t xml:space="preserve">2026-04-28 11:02:06 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Source data</t>

--- a/output/tables/answers_eligibility_by_filing_match.xlsx
+++ b/output/tables/answers_eligibility_by_filing_match.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-09 13:58:21 EDT</t>
+    <t xml:space="preserve">2026-06-09 16:49:21 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Universe</t>
